--- a/exports/HINDALCO_full_report.xlsx
+++ b/exports/HINDALCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.19</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>507.6</v>
+        <v>484.85</v>
       </c>
       <c r="I2" t="n">
         <v>485.5632209419965</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>2.89</v>
+        <v>-1.72</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55</v>
+        <v>2.56</v>
       </c>
       <c r="M2" t="n">
-        <v>0.46</v>
+        <v>1.7</v>
       </c>
       <c r="N2" t="n">
-        <v>1.78</v>
+        <v>5.84</v>
       </c>
       <c r="O2" t="n">
         <v>0.12</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.16</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44594.55208333334</v>
+        <v>44595.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>513.75</v>
+        <v>515.3</v>
       </c>
       <c r="I3" t="n">
         <v>513.854594162238</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.96</v>
+        <v>-6.28</v>
       </c>
       <c r="L3" t="n">
         <v>6.91</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.85</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44613.38541666666</v>
+        <v>44613.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>519.35</v>
+        <v>511.7</v>
       </c>
       <c r="I4" t="n">
         <v>516.7838936538523</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>0.79</v>
+        <v>-0.7</v>
       </c>
       <c r="L4" t="n">
         <v>1.2</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>6.78</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44616.55208333334</v>
+        <v>44617.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>517.4</v>
+        <v>540</v>
       </c>
       <c r="I5" t="n">
         <v>539.6680090909318</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.11</v>
+        <v>-5.53</v>
       </c>
       <c r="L5" t="n">
-        <v>3.07</v>
+        <v>6.88</v>
       </c>
       <c r="M5" t="n">
-        <v>0.64</v>
+        <v>1.47</v>
       </c>
       <c r="N5" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="O5" t="n">
         <v>-3.53</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>7.92</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44650.55208333334</v>
+        <v>44651.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>600.45</v>
+        <v>573.7</v>
       </c>
       <c r="I6" t="n">
         <v>596.9911641695544</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K6" t="n">
-        <v>11.19</v>
+        <v>6.24</v>
       </c>
       <c r="L6" t="n">
         <v>3.06</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.449999999999999</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44699.38541666666</v>
+        <v>44699.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>428.8</v>
+        <v>435.9</v>
       </c>
       <c r="I7" t="n">
         <v>432.8263917255952</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>48</v>
+        <v>48.16666666666666</v>
       </c>
       <c r="K7" t="n">
-        <v>25.26</v>
+        <v>24.02</v>
       </c>
       <c r="L7" t="n">
         <v>4.64</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>10.76</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>400.5</v>
+        <v>385.55</v>
       </c>
       <c r="I8" t="n">
         <v>388.993094388837</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-8.119999999999999</v>
+        <v>-11.55</v>
       </c>
       <c r="L8" t="n">
-        <v>10.6</v>
+        <v>12.17</v>
       </c>
       <c r="M8" t="n">
         <v>3.17</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.32</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44746.55208333334</v>
+        <v>44747.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>340.2</v>
+        <v>353.65</v>
       </c>
       <c r="I9" t="n">
         <v>351.3836934501061</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K9" t="n">
-        <v>11.76</v>
+        <v>8.27</v>
       </c>
       <c r="L9" t="n">
         <v>1.57</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10.35</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44806.38541666666</v>
+        <v>44806.55208333334</v>
       </c>
       <c r="H10" t="n">
-        <v>416.05</v>
+        <v>414.75</v>
       </c>
       <c r="I10" t="n">
         <v>415.5618610300097</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>59</v>
+        <v>59.16666666666666</v>
       </c>
       <c r="K10" t="n">
-        <v>17.64</v>
+        <v>17.28</v>
       </c>
       <c r="L10" t="n">
         <v>7.31</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>6.71</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>381</v>
+        <v>394.85</v>
       </c>
       <c r="I11" t="n">
         <v>393.1998549372792</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31</v>
+        <v>31.83333333333333</v>
       </c>
       <c r="K11" t="n">
-        <v>8.140000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="L11" t="n">
         <v>7.99</v>
       </c>
       <c r="M11" t="n">
-        <v>1.89</v>
+        <v>3.94</v>
       </c>
       <c r="N11" t="n">
         <v>5.18</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44914.55208333334</v>
+        <v>44915.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>459.55</v>
+        <v>448.5</v>
       </c>
       <c r="I12" t="n">
         <v>454.5866206798955</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>76.16666666666667</v>
+        <v>77</v>
       </c>
       <c r="K12" t="n">
-        <v>16.39</v>
+        <v>13.59</v>
       </c>
       <c r="L12" t="n">
         <v>3.71</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>103</v>
+        <v>104</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>6.28</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44922.38541666666</v>
+        <v>44922.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>463.2</v>
+        <v>470.7</v>
       </c>
       <c r="I13" t="n">
         <v>465.9967513429215</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.28</v>
+        <v>-4.95</v>
       </c>
       <c r="L13" t="n">
-        <v>3.43</v>
+        <v>5.32</v>
       </c>
       <c r="M13" t="n">
         <v>1.25</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>7.79</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44953.55208333334</v>
+        <v>44956.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>478.05</v>
+        <v>465.5</v>
       </c>
       <c r="I14" t="n">
         <v>474.6319436959804</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>31</v>
+        <v>33.83333333333334</v>
       </c>
       <c r="K14" t="n">
-        <v>1.56</v>
+        <v>-1.1</v>
       </c>
       <c r="L14" t="n">
         <v>3.28</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.68</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>405</v>
+        <v>412.8</v>
       </c>
       <c r="I15" t="n">
         <v>411.0103062949885</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>66.16666666666667</v>
+        <v>70</v>
       </c>
       <c r="K15" t="n">
-        <v>13</v>
+        <v>11.32</v>
       </c>
       <c r="L15" t="n">
         <v>3.82</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>90</v>
+        <v>91</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,19 +1523,19 @@
         <v>5.69</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>45056.55208333334</v>
+        <v>45057.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>438.05</v>
+        <v>421.25</v>
       </c>
       <c r="I16" t="n">
         <v>428.8805580963638</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K16" t="n">
-        <v>6.12</v>
+        <v>2.05</v>
       </c>
       <c r="L16" t="n">
         <v>1.74</v>
@@ -1353,7 +1544,7 @@
         <v>1.01</v>
       </c>
       <c r="N16" t="n">
-        <v>2.2</v>
+        <v>3.85</v>
       </c>
       <c r="O16" t="n">
         <v>1.41</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>6.46</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>413.05</v>
+        <v>423.4</v>
       </c>
       <c r="I17" t="n">
         <v>419.7007377276568</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K17" t="n">
-        <v>1.95</v>
+        <v>-0.51</v>
       </c>
       <c r="L17" t="n">
         <v>3.03</v>
       </c>
       <c r="M17" t="n">
-        <v>0.74</v>
+        <v>0.96</v>
       </c>
       <c r="N17" t="n">
         <v>2.32</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>5.53</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45099.55208333334</v>
+        <v>45100.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>420.45</v>
+        <v>411.5</v>
       </c>
       <c r="I18" t="n">
         <v>412.9225138203609</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7</v>
+        <v>-2.81</v>
       </c>
       <c r="L18" t="n">
         <v>4.49</v>
       </c>
       <c r="M18" t="n">
-        <v>0.76</v>
+        <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>1.76</v>
+        <v>3.02</v>
       </c>
       <c r="O18" t="n">
         <v>1.61</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,22 +1730,22 @@
         <v>5.14</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45114.55208333334</v>
+        <v>45117.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>422.15</v>
+        <v>428.2</v>
       </c>
       <c r="I19" t="n">
         <v>428.1368501577936</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.59</v>
+        <v>-4.06</v>
       </c>
       <c r="L19" t="n">
-        <v>4.24</v>
+        <v>6</v>
       </c>
       <c r="M19" t="n">
         <v>0.83</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>4.08</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45152.55208333334</v>
+        <v>45154.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>448.85</v>
+        <v>444.35</v>
       </c>
       <c r="I20" t="n">
         <v>445.9122656323852</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>35.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K20" t="n">
-        <v>4.82</v>
+        <v>3.77</v>
       </c>
       <c r="L20" t="n">
         <v>1.39</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,28 +1868,28 @@
         <v>5.37</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45160.55208333334</v>
+        <v>45161.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>451</v>
+        <v>463.25</v>
       </c>
       <c r="I21" t="n">
         <v>462.1652208766259</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.5</v>
+        <v>-4.25</v>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>4.71</v>
       </c>
       <c r="M21" t="n">
         <v>0.87</v>
       </c>
       <c r="N21" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="O21" t="n">
         <v>-1.08</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>5.75</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45191.55208333334</v>
+        <v>45194.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>477.8</v>
+        <v>471.15</v>
       </c>
       <c r="I22" t="n">
         <v>473.6765230960223</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K22" t="n">
-        <v>3.14</v>
+        <v>1.71</v>
       </c>
       <c r="L22" t="n">
         <v>3.83</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>5.74</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45197.55208333334</v>
+        <v>45198.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>468</v>
+        <v>490.7</v>
       </c>
       <c r="I23" t="n">
         <v>489.7732287317783</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K23" t="n">
-        <v>0.67</v>
+        <v>-4.15</v>
       </c>
       <c r="L23" t="n">
-        <v>1.79</v>
+        <v>4.32</v>
       </c>
       <c r="M23" t="n">
-        <v>0.22</v>
+        <v>2.14</v>
       </c>
       <c r="N23" t="n">
-        <v>0.98</v>
+        <v>5.34</v>
       </c>
       <c r="O23" t="n">
         <v>-1.84</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>7.08</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>472.7</v>
+        <v>460.8</v>
       </c>
       <c r="I24" t="n">
         <v>467.2531279955021</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.67</v>
+        <v>-6.09</v>
       </c>
       <c r="L24" t="n">
-        <v>5.32</v>
+        <v>6.15</v>
       </c>
       <c r="M24" t="n">
         <v>2.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.62</v>
+        <v>3.27</v>
       </c>
       <c r="O24" t="n">
         <v>5.34</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.4</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45232.55208333334</v>
+        <v>45233.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>475.1</v>
+        <v>479.15</v>
       </c>
       <c r="I25" t="n">
         <v>478.8146952854927</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.1</v>
+        <v>-3.98</v>
       </c>
       <c r="L25" t="n">
-        <v>3.26</v>
+        <v>4.48</v>
       </c>
       <c r="M25" t="n">
         <v>1.91</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>4.68</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45296.38541666666</v>
+        <v>45296.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>591.2</v>
+        <v>587.95</v>
       </c>
       <c r="I26" t="n">
         <v>588.305863290297</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>63</v>
+        <v>63.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>23.39</v>
+        <v>22.71</v>
       </c>
       <c r="L26" t="n">
         <v>1.02</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.58</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>569.2</v>
+        <v>581.55</v>
       </c>
       <c r="I27" t="n">
         <v>570.844115899757</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K27" t="n">
-        <v>3.19</v>
+        <v>1.09</v>
       </c>
       <c r="L27" t="n">
         <v>0.77</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.08</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45334.55208333334</v>
+        <v>45335.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>583.9</v>
+        <v>501</v>
       </c>
       <c r="I28" t="n">
         <v>563.3029038361874</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4</v>
+        <v>-13.85</v>
       </c>
       <c r="L28" t="n">
-        <v>2.46</v>
+        <v>14.65</v>
       </c>
       <c r="M28" t="n">
-        <v>0.34</v>
+        <v>7.69</v>
       </c>
       <c r="N28" t="n">
-        <v>1.51</v>
+        <v>12.75</v>
       </c>
       <c r="O28" t="n">
         <v>0.05</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>15.83</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45357.55208333334</v>
+        <v>45358.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>527.2</v>
+        <v>537.05</v>
       </c>
       <c r="I29" t="n">
         <v>530.3383041392082</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K29" t="n">
-        <v>-5.23</v>
+        <v>-7.2</v>
       </c>
       <c r="L29" t="n">
         <v>7.78</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>5.51</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>514.8</v>
+        <v>506.65</v>
       </c>
       <c r="I30" t="n">
         <v>514.0245407212974</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.14</v>
+        <v>-5.66</v>
       </c>
       <c r="L30" t="n">
-        <v>5.5</v>
+        <v>6.68</v>
       </c>
       <c r="M30" t="n">
         <v>0.01</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,25 +2558,25 @@
         <v>6.17</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45371.55208333334</v>
+        <v>45372.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>526.45</v>
+        <v>538.8</v>
       </c>
       <c r="I31" t="n">
         <v>537.8951331994811</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.91</v>
+        <v>-6.35</v>
       </c>
       <c r="L31" t="n">
-        <v>6.53</v>
+        <v>7.72</v>
       </c>
       <c r="M31" t="n">
-        <v>1.06</v>
+        <v>2.27</v>
       </c>
       <c r="N31" t="n">
         <v>3.82</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>5.81</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>639</v>
+        <v>612.25</v>
       </c>
       <c r="I32" t="n">
         <v>615.1162469936702</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K32" t="n">
-        <v>18.6</v>
+        <v>13.63</v>
       </c>
       <c r="L32" t="n">
         <v>0.84</v>
@@ -2265,7 +2648,7 @@
         <v>1.26</v>
       </c>
       <c r="N32" t="n">
-        <v>1.42</v>
+        <v>2.89</v>
       </c>
       <c r="O32" t="n">
         <v>2.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>3</v>
+      </c>
+      <c r="U32" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>10.02</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45429.55208333334</v>
+        <v>45430.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>655.65</v>
+        <v>659.8</v>
       </c>
       <c r="I33" t="n">
         <v>658.4920718645276</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.09</v>
+        <v>-7.77</v>
       </c>
       <c r="L33" t="n">
         <v>8.779999999999999</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>4.79</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>698</v>
+        <v>636</v>
       </c>
       <c r="I34" t="n">
         <v>663.1248346656513</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K34" t="n">
-        <v>5.79</v>
+        <v>-3.61</v>
       </c>
       <c r="L34" t="n">
-        <v>0.35</v>
+        <v>9.93</v>
       </c>
       <c r="M34" t="n">
         <v>1.51</v>
       </c>
       <c r="N34" t="n">
-        <v>1.68</v>
+        <v>6.88</v>
       </c>
       <c r="O34" t="n">
         <v>0.63</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>2</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>12.78</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45477.55208333334</v>
+        <v>45478.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>693.5</v>
+        <v>700.5</v>
       </c>
       <c r="I35" t="n">
         <v>698.7926262297434</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.039999999999999</v>
+        <v>-10.14</v>
       </c>
       <c r="L35" t="n">
         <v>10.97</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>4.81</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45491.55208333334</v>
+        <v>45492.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>690</v>
+        <v>664.85</v>
       </c>
       <c r="I36" t="n">
         <v>675.0652872629088</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.5</v>
+        <v>-5.09</v>
       </c>
       <c r="L36" t="n">
-        <v>2.34</v>
+        <v>5.7</v>
       </c>
       <c r="M36" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="N36" t="n">
-        <v>2.56</v>
+        <v>3.91</v>
       </c>
       <c r="O36" t="n">
         <v>0.6899999999999999</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>6.42</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45520.55208333334</v>
+        <v>45523.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>633.7</v>
+        <v>655.8</v>
       </c>
       <c r="I37" t="n">
         <v>653.3261981994769</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K37" t="n">
-        <v>4.69</v>
+        <v>1.36</v>
       </c>
       <c r="L37" t="n">
         <v>3.92</v>
@@ -2550,7 +2993,7 @@
         <v>1.88</v>
       </c>
       <c r="N37" t="n">
-        <v>3.13</v>
+        <v>4.07</v>
       </c>
       <c r="O37" t="n">
         <v>-3.91</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,25 +3041,25 @@
         <v>7.44</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45538.55208333334</v>
+        <v>45539.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>679</v>
+        <v>665</v>
       </c>
       <c r="I38" t="n">
         <v>673.6693169788346</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K38" t="n">
-        <v>3.54</v>
+        <v>1.4</v>
       </c>
       <c r="L38" t="n">
         <v>2.94</v>
       </c>
       <c r="M38" t="n">
-        <v>1.1</v>
+        <v>1.82</v>
       </c>
       <c r="N38" t="n">
         <v>2.64</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>5.47</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45548.55208333334</v>
+        <v>45551.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>673.8</v>
+        <v>683.4</v>
       </c>
       <c r="I39" t="n">
         <v>678.5452091449938</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
-        <v>-1.32</v>
+        <v>-2.77</v>
       </c>
       <c r="L39" t="n">
         <v>3.22</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>5.24</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45569.55208333334</v>
+        <v>45572.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>747.05</v>
+        <v>723.9</v>
       </c>
       <c r="I40" t="n">
         <v>724.0961895874643</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K40" t="n">
-        <v>9.31</v>
+        <v>5.93</v>
       </c>
       <c r="L40" t="n">
         <v>2.22</v>
@@ -2721,7 +3200,7 @@
         <v>1.32</v>
       </c>
       <c r="N40" t="n">
-        <v>1.97</v>
+        <v>2.39</v>
       </c>
       <c r="O40" t="n">
         <v>1.59</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45631.55208333334</v>
+        <v>45632.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>670.3</v>
+        <v>675.3</v>
       </c>
       <c r="I41" t="n">
         <v>674.2234857964957</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K41" t="n">
-        <v>7.4</v>
+        <v>6.71</v>
       </c>
       <c r="L41" t="n">
         <v>5.74</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>3</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.53</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>652.9</v>
+        <v>640.75</v>
       </c>
       <c r="I42" t="n">
         <v>645.9314332915648</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.32</v>
+        <v>-5.12</v>
       </c>
       <c r="L42" t="n">
-        <v>4.04</v>
+        <v>5.19</v>
       </c>
       <c r="M42" t="n">
         <v>0.87</v>
       </c>
       <c r="N42" t="n">
-        <v>1.82</v>
+        <v>2.14</v>
       </c>
       <c r="O42" t="n">
         <v>-0.04</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>5.73</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45672.55208333334</v>
+        <v>45673.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>591.25</v>
+        <v>603.3</v>
       </c>
       <c r="I43" t="n">
         <v>593.8844588518931</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K43" t="n">
-        <v>7.73</v>
+        <v>5.84</v>
       </c>
       <c r="L43" t="n">
         <v>2.01</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>6.02</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>607.6</v>
+        <v>592.95</v>
       </c>
       <c r="I44" t="n">
         <v>593.1919782889854</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K44" t="n">
-        <v>0.71</v>
+        <v>-1.72</v>
       </c>
       <c r="L44" t="n">
         <v>2.11</v>
       </c>
       <c r="M44" t="n">
-        <v>0.59</v>
+        <v>1.24</v>
       </c>
       <c r="N44" t="n">
-        <v>1.07</v>
+        <v>3.64</v>
       </c>
       <c r="O44" t="n">
         <v>1.9</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>5.67</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45694.55208333334</v>
+        <v>45695.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>596.95</v>
+        <v>609.8</v>
       </c>
       <c r="I45" t="n">
         <v>604.5425617808775</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.67</v>
+        <v>-2.84</v>
       </c>
       <c r="L45" t="n">
-        <v>2.34</v>
+        <v>2.98</v>
       </c>
       <c r="M45" t="n">
         <v>0.96</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.22</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="I46" t="n">
         <v>675.4384742225716</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K46" t="n">
-        <v>11.84</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="L46" t="n">
         <v>3.85</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>3</v>
+      </c>
+      <c r="U46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>6.4</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>601.8</v>
+        <v>614.35</v>
       </c>
       <c r="I47" t="n">
         <v>610.5326436386977</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K47" t="n">
-        <v>9.369999999999999</v>
+        <v>7.48</v>
       </c>
       <c r="L47" t="n">
         <v>2.88</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>9.1</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45806.55208333334</v>
+        <v>45807.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>651</v>
+        <v>636.05</v>
       </c>
       <c r="I48" t="n">
         <v>636.287439138584</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K48" t="n">
-        <v>5.97</v>
+        <v>3.53</v>
       </c>
       <c r="L48" t="n">
         <v>2.01</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>3</v>
+      </c>
+      <c r="U48" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.61</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45817.55208333334</v>
+        <v>45818.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>650</v>
+        <v>660.85</v>
       </c>
       <c r="I49" t="n">
         <v>656.978767047057</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-2.19</v>
+        <v>-3.9</v>
       </c>
       <c r="L49" t="n">
-        <v>2.92</v>
+        <v>4.32</v>
       </c>
       <c r="M49" t="n">
         <v>0.85</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>4.18</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45846.55208333334</v>
+        <v>45847.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>687.3</v>
+        <v>672.75</v>
       </c>
       <c r="I50" t="n">
         <v>675.9648076797242</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K50" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="L50" t="n">
         <v>3.91</v>
@@ -3291,7 +3890,7 @@
         <v>2.46</v>
       </c>
       <c r="N50" t="n">
-        <v>1.48</v>
+        <v>2.07</v>
       </c>
       <c r="O50" t="n">
         <v>1.08</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.5</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45861.38541666666</v>
+        <v>45861.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>691.1</v>
+        <v>695.5</v>
       </c>
       <c r="I51" t="n">
         <v>691.9587527084255</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.73</v>
+        <v>-3.38</v>
       </c>
       <c r="L51" t="n">
-        <v>3.3</v>
+        <v>3.46</v>
       </c>
       <c r="M51" t="n">
         <v>0.68</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>3.45</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45869.55208333334</v>
+        <v>45870.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>683.7</v>
+        <v>675.95</v>
       </c>
       <c r="I52" t="n">
         <v>677.4501448650208</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.7</v>
+        <v>-2.81</v>
       </c>
       <c r="L52" t="n">
-        <v>2.95</v>
+        <v>3.54</v>
       </c>
       <c r="M52" t="n">
         <v>1.73</v>
       </c>
       <c r="N52" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="O52" t="n">
         <v>0.72</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>4.17</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>694.4</v>
+        <v>711.6</v>
       </c>
       <c r="I53" t="n">
         <v>701.4135079579017</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K53" t="n">
-        <v>-2.73</v>
+        <v>-5.27</v>
       </c>
       <c r="L53" t="n">
-        <v>4.29</v>
+        <v>5.49</v>
       </c>
       <c r="M53" t="n">
         <v>1.05</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>6.39</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45965.55208333334</v>
+        <v>45967.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>830.85</v>
+        <v>778.95</v>
       </c>
       <c r="I54" t="n">
         <v>824.6127454579382</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>80</v>
       </c>
       <c r="K54" t="n">
-        <v>16.76</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L54" t="n">
         <v>2.05</v>
       </c>
       <c r="M54" t="n">
-        <v>0.82</v>
+        <v>5.16</v>
       </c>
       <c r="N54" t="n">
-        <v>1.85</v>
+        <v>5.33</v>
       </c>
       <c r="O54" t="n">
         <v>2.99</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>107</v>
+        <v>108</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>4</v>
+      </c>
+      <c r="U54" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.74</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45988.55208333334</v>
+        <v>45989.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>807.1</v>
+        <v>810.45</v>
       </c>
       <c r="I55" t="n">
         <v>808.5393298494711</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K55" t="n">
-        <v>-3.61</v>
+        <v>-4.04</v>
       </c>
       <c r="L55" t="n">
         <v>4.82</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>4.08</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>937.85</v>
+        <v>906.6</v>
       </c>
       <c r="I56" t="n">
         <v>911.684014378135</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>40.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K56" t="n">
-        <v>15.72</v>
+        <v>11.86</v>
       </c>
       <c r="L56" t="n">
         <v>1.17</v>
       </c>
       <c r="M56" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="N56" t="n">
-        <v>1.35</v>
+        <v>3.72</v>
       </c>
       <c r="O56" t="n">
         <v>0.3</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>6.37</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46035.55208333334</v>
+        <v>46036.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>935</v>
+        <v>954.65</v>
       </c>
       <c r="I57" t="n">
         <v>943.8262322233826</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K57" t="n">
-        <v>-3.13</v>
+        <v>-5.3</v>
       </c>
       <c r="L57" t="n">
-        <v>3.45</v>
+        <v>5.78</v>
       </c>
       <c r="M57" t="n">
         <v>0.66</v>
       </c>
       <c r="N57" t="n">
-        <v>1.92</v>
+        <v>2.24</v>
       </c>
       <c r="O57" t="n">
         <v>-3.72</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>5.56</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46051.55208333334</v>
+        <v>46052.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>1027</v>
+        <v>957.4</v>
       </c>
       <c r="I58" t="n">
         <v>970.7363647751557</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K58" t="n">
-        <v>7.58</v>
+        <v>0.29</v>
       </c>
       <c r="L58" t="n">
         <v>3.03</v>
       </c>
       <c r="M58" t="n">
-        <v>0.04</v>
+        <v>2.63</v>
       </c>
       <c r="N58" t="n">
-        <v>2.5</v>
+        <v>6.7</v>
       </c>
       <c r="O58" t="n">
         <v>2.24</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>9.41</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46085.55208333334</v>
+        <v>46086.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>922.5</v>
+        <v>977.7</v>
       </c>
       <c r="I59" t="n">
         <v>949.4474513168529</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K59" t="n">
-        <v>3.65</v>
+        <v>-2.12</v>
       </c>
       <c r="L59" t="n">
         <v>4.45</v>
@@ -3804,7 +4511,7 @@
         <v>2.61</v>
       </c>
       <c r="N59" t="n">
-        <v>3.34</v>
+        <v>3.71</v>
       </c>
       <c r="O59" t="n">
         <v>-6.7</v>
@@ -3813,7 +4520,19 @@
         <v>1</v>
       </c>
       <c r="Q59" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46100.55208333334</v>
+        <v>46101.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>900</v>
+        <v>888.6</v>
       </c>
       <c r="I60" t="n">
         <v>895.121236528601</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K60" t="n">
-        <v>-7.95</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>8.75</v>
+        <v>10.5</v>
       </c>
       <c r="M60" t="n">
         <v>2.39</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>7.83</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46113.55208333334</v>
+        <v>46114.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>904.65</v>
+        <v>910.4</v>
       </c>
       <c r="I61" t="n">
         <v>909.3833178357982</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K61" t="n">
-        <v>-1.81</v>
+        <v>-2.45</v>
       </c>
       <c r="L61" t="n">
         <v>3.81</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.31</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46153.38541666666</v>
+        <v>46153.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>1030.2</v>
+        <v>1022.3</v>
       </c>
       <c r="I62" t="n">
         <v>1026.291893630846</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>39</v>
+        <v>39.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>13.16</v>
+        <v>12.29</v>
       </c>
       <c r="L62" t="n">
         <v>2.81</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>5.31</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46154.55208333334</v>
+        <v>46155.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>1042</v>
+        <v>1077.2</v>
       </c>
       <c r="I63" t="n">
         <v>1076.573189732934</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.93</v>
+        <v>-5.37</v>
       </c>
       <c r="L63" t="n">
-        <v>3.16</v>
+        <v>5.79</v>
       </c>
       <c r="M63" t="n">
-        <v>0.48</v>
+        <v>0.58</v>
       </c>
       <c r="N63" t="n">
-        <v>1.93</v>
+        <v>3.55</v>
       </c>
       <c r="O63" t="n">
         <v>-2.13</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.48</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46161.38541666666</v>
+        <v>46161.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>1050.5</v>
+        <v>1046.6</v>
       </c>
       <c r="I64" t="n">
         <v>1047.01996992514</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>-2.48</v>
+        <v>-2.84</v>
       </c>
       <c r="L64" t="n">
         <v>3.72</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.37</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46164.38541666666</v>
+        <v>46164.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>1095.5</v>
+        <v>1110</v>
       </c>
       <c r="I65" t="n">
         <v>1102.779546313014</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>2.833333333333333</v>
+        <v>3</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.67</v>
+        <v>-6.06</v>
       </c>
       <c r="L65" t="n">
-        <v>6.14</v>
+        <v>6.54</v>
       </c>
       <c r="M65" t="n">
         <v>1.26</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,28 +4973,28 @@
         <v>5.63</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46178.55208333334</v>
+        <v>46181.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>1090.1</v>
+        <v>1075.7</v>
       </c>
       <c r="I66" t="n">
         <v>1087.404927451713</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>14</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.79</v>
+        <v>-3.09</v>
       </c>
       <c r="L66" t="n">
-        <v>2.59</v>
+        <v>4.77</v>
       </c>
       <c r="M66" t="n">
-        <v>0.48</v>
+        <v>2.67</v>
       </c>
       <c r="N66" t="n">
-        <v>3.12</v>
+        <v>3.4</v>
       </c>
       <c r="O66" t="n">
         <v>0.91</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>5.32</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>969.5</v>
+        <v>978.3</v>
       </c>
       <c r="I67" t="n">
         <v>970.0515429276612</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>53</v>
       </c>
       <c r="K67" t="n">
-        <v>9.869999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="L67" t="n">
         <v>0.63</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>3.63</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46254.38541666666</v>
+        <v>46254.55208333334</v>
       </c>
       <c r="H68" t="n">
-        <v>1028.2</v>
+        <v>1022.95</v>
       </c>
       <c r="I68" t="n">
         <v>1023.440691232411</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K68" t="n">
-        <v>5.1</v>
+        <v>4.56</v>
       </c>
       <c r="L68" t="n">
         <v>0.74</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>91</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23.9</v>
+        <v>25.1</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.2</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.4</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7374,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7384,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7394,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.14</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.03</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.18</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>25.26</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>55.2</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.68</v>
+        <v>4.56</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.22</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7474,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10.97</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7494,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.45</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5.11</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.14</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>9.369999999999999</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
